--- a/Analysis/symmetric_gate_metrics.xlsx
+++ b/Analysis/symmetric_gate_metrics.xlsx
@@ -483,13 +483,13 @@
         <v>195</v>
       </c>
       <c r="F2" t="n">
-        <v>0.144</v>
+        <v>0.1248</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3668</v>
+        <v>0.3908</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7221</v>
+        <v>0.7292</v>
       </c>
     </row>
     <row r="3">
@@ -517,13 +517,13 @@
         <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1021</v>
+        <v>-0.1105</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1978</v>
+        <v>0.26</v>
       </c>
       <c r="H3" t="n">
-        <v>0.639</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="4">
@@ -551,13 +551,13 @@
         <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0293</v>
+        <v>0.0421</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3171</v>
+        <v>0.3538</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6308</v>
+        <v>0.6768999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -585,13 +585,13 @@
         <v>60</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5577</v>
+        <v>0.4889</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6194</v>
+        <v>0.5833</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9192</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="6">
@@ -619,13 +619,13 @@
         <v>195</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3067</v>
+        <v>0.2533</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5354</v>
+        <v>0.4836</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8113</v>
+        <v>0.8173</v>
       </c>
     </row>
     <row r="7">
@@ -653,13 +653,13 @@
         <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0419</v>
+        <v>0.0305</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3286</v>
+        <v>0.2971</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6629</v>
+        <v>0.7171</v>
       </c>
     </row>
     <row r="8">
@@ -687,13 +687,13 @@
         <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4174</v>
+        <v>0.2879</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7015</v>
+        <v>0.6019</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9015</v>
+        <v>0.8425</v>
       </c>
     </row>
     <row r="9">
@@ -721,13 +721,13 @@
         <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4956</v>
+        <v>0.4756</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5967</v>
+        <v>0.5733</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8867</v>
+        <v>0.9067</v>
       </c>
     </row>
     <row r="10">
@@ -755,13 +755,13 @@
         <v>195</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8973</v>
+        <v>0.8582</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9076</v>
+        <v>0.888</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9774</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="11">
@@ -789,13 +789,13 @@
         <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9198</v>
+        <v>0.795</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9198</v>
+        <v>0.8477</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9885</v>
+        <v>0.9454</v>
       </c>
     </row>
     <row r="12">
@@ -823,10 +823,10 @@
         <v>65</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9754</v>
+        <v>0.9467</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9846</v>
+        <v>0.9692</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -857,13 +857,13 @@
         <v>60</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7867</v>
+        <v>0.8356</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8467</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9567</v>
       </c>
     </row>
     <row r="14">
@@ -891,13 +891,13 @@
         <v>195</v>
       </c>
       <c r="F14" t="n">
-        <v>0.144</v>
+        <v>0.1248</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3668</v>
+        <v>0.3908</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7221</v>
+        <v>0.7292</v>
       </c>
     </row>
     <row r="15">
@@ -925,13 +925,13 @@
         <v>70</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1021</v>
+        <v>-0.1105</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1978</v>
+        <v>0.26</v>
       </c>
       <c r="H15" t="n">
-        <v>0.639</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="16">
@@ -959,13 +959,13 @@
         <v>65</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0293</v>
+        <v>0.0421</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3171</v>
+        <v>0.3538</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6308</v>
+        <v>0.6768999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -993,13 +993,13 @@
         <v>60</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5577</v>
+        <v>0.4889</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6194</v>
+        <v>0.5833</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9192</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="18">
@@ -1027,13 +1027,13 @@
         <v>195</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3067</v>
+        <v>0.2533</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5354</v>
+        <v>0.4836</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8113</v>
+        <v>0.8173</v>
       </c>
     </row>
     <row r="19">
@@ -1061,13 +1061,13 @@
         <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0419</v>
+        <v>0.0305</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3286</v>
+        <v>0.2971</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6629</v>
+        <v>0.7171</v>
       </c>
     </row>
     <row r="20">
@@ -1095,13 +1095,13 @@
         <v>65</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4174</v>
+        <v>0.2879</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7015</v>
+        <v>0.6019</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9015</v>
+        <v>0.8425</v>
       </c>
     </row>
     <row r="21">
@@ -1129,13 +1129,13 @@
         <v>60</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4956</v>
+        <v>0.4756</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5967</v>
+        <v>0.5733</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8867</v>
+        <v>0.9067</v>
       </c>
     </row>
     <row r="22">
@@ -1163,13 +1163,13 @@
         <v>195</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8973</v>
+        <v>0.8582</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9076</v>
+        <v>0.888</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9774</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="23">
@@ -1197,13 +1197,13 @@
         <v>70</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9198</v>
+        <v>0.795</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9198</v>
+        <v>0.8477</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9885</v>
+        <v>0.9454</v>
       </c>
     </row>
     <row r="24">
@@ -1231,10 +1231,10 @@
         <v>65</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9754</v>
+        <v>0.9467</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9846</v>
+        <v>0.9692</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -1265,13 +1265,13 @@
         <v>60</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7867</v>
+        <v>0.8356</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8467</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9567</v>
       </c>
     </row>
     <row r="26">
@@ -1296,16 +1296,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1344</v>
+        <v>0.1233</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3604</v>
+        <v>0.3896</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7176</v>
+        <v>0.7275</v>
       </c>
     </row>
     <row r="27">
@@ -1330,16 +1330,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1059</v>
+        <v>-0.1111</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2</v>
+        <v>0.2609</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6324</v>
+        <v>0.6377</v>
       </c>
     </row>
     <row r="28">
@@ -1364,16 +1364,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0215</v>
+        <v>0.0333</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3097</v>
+        <v>0.3469</v>
       </c>
       <c r="H28" t="n">
-        <v>0.629</v>
+        <v>0.6719000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1398,16 +1398,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.4889</v>
       </c>
       <c r="G29" t="n">
-        <v>0.607</v>
+        <v>0.5833</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="30">
@@ -1432,16 +1432,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F30" t="n">
-        <v>0.297</v>
+        <v>0.2553</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5337</v>
+        <v>0.487</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8032</v>
+        <v>0.8155</v>
       </c>
     </row>
     <row r="31">
@@ -1466,16 +1466,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0431</v>
+        <v>0.0357</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3382</v>
+        <v>0.3014</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6529</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="32">
@@ -1500,16 +1500,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3892</v>
+        <v>0.2854</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6871</v>
+        <v>0.6062</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8968</v>
+        <v>0.8406</v>
       </c>
     </row>
     <row r="33">
@@ -1534,16 +1534,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4994</v>
+        <v>0.4756</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6</v>
+        <v>0.5733</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8807</v>
+        <v>0.9067</v>
       </c>
     </row>
     <row r="34">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8945</v>
+        <v>0.8577</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9059</v>
+        <v>0.887</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9765</v>
+        <v>0.9668</v>
       </c>
     </row>
     <row r="35">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9216</v>
+        <v>0.7952</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9235</v>
+        <v>0.8464</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9882</v>
+        <v>0.9449</v>
       </c>
     </row>
     <row r="36">
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9742</v>
+        <v>0.9458</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9839</v>
+        <v>0.9688</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
@@ -1670,16 +1670,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7754</v>
+        <v>0.8356</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8</v>
+        <v>0.8467</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9368</v>
+        <v>0.9567</v>
       </c>
     </row>
     <row r="38">
@@ -1707,13 +1707,13 @@
         <v>195</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1761</v>
+        <v>0.1788</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3621</v>
+        <v>0.3979</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6974</v>
+        <v>0.7026</v>
       </c>
     </row>
     <row r="39">
@@ -1741,13 +1741,13 @@
         <v>70</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.0324</v>
+        <v>-0.2</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2543</v>
+        <v>0.1914</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6143</v>
+        <v>0.5229</v>
       </c>
     </row>
     <row r="40">
@@ -1775,13 +1775,13 @@
         <v>65</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.0215</v>
+        <v>0.1097</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2492</v>
+        <v>0.3631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5754</v>
+        <v>0.6892</v>
       </c>
     </row>
     <row r="41">
@@ -1809,10 +1809,10 @@
         <v>60</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6333</v>
+        <v>0.6956</v>
       </c>
       <c r="G41" t="n">
-        <v>0.61</v>
+        <v>0.6767</v>
       </c>
       <c r="H41" t="n">
         <v>0.9267</v>
@@ -1843,13 +1843,13 @@
         <v>195</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3099</v>
+        <v>0.2985</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4871</v>
+        <v>0.4749</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7958</v>
+        <v>0.7713</v>
       </c>
     </row>
     <row r="43">
@@ -1877,13 +1877,13 @@
         <v>70</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.1162</v>
+        <v>-0.1181</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1528</v>
+        <v>0.1514</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6657</v>
+        <v>0.5857</v>
       </c>
     </row>
     <row r="44">
@@ -1911,13 +1911,13 @@
         <v>65</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3441</v>
+        <v>0.3026</v>
       </c>
       <c r="G44" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5446</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7611</v>
+        <v>0.7907999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1945,13 +1945,13 @@
         <v>60</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7667</v>
+        <v>0.78</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7933</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9833</v>
+        <v>0.9667</v>
       </c>
     </row>
     <row r="46">
@@ -1979,13 +1979,13 @@
         <v>195</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9234</v>
+        <v>0.8913</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9313</v>
+        <v>0.9015</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
     </row>
     <row r="47">
@@ -2013,13 +2013,13 @@
         <v>70</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9771</v>
+        <v>0.8724</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9657</v>
+        <v>0.8829</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0.9714</v>
       </c>
     </row>
     <row r="48">
@@ -2047,10 +2047,10 @@
         <v>65</v>
       </c>
       <c r="F48" t="n">
-        <v>0.959</v>
+        <v>0.9446</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9692</v>
+        <v>0.9538</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -2081,13 +2081,13 @@
         <v>60</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8222</v>
+        <v>0.8556</v>
       </c>
       <c r="G49" t="n">
-        <v>0.85</v>
+        <v>0.8667</v>
       </c>
       <c r="H49" t="n">
-        <v>0.95</v>
+        <v>0.9667</v>
       </c>
     </row>
     <row r="50">
@@ -2115,13 +2115,13 @@
         <v>195</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1761</v>
+        <v>0.1788</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3621</v>
+        <v>0.3979</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6974</v>
+        <v>0.7026</v>
       </c>
     </row>
     <row r="51">
@@ -2149,13 +2149,13 @@
         <v>70</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0324</v>
+        <v>-0.2</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2543</v>
+        <v>0.1914</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6143</v>
+        <v>0.5229</v>
       </c>
     </row>
     <row r="52">
@@ -2183,13 +2183,13 @@
         <v>65</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0215</v>
+        <v>0.1097</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2492</v>
+        <v>0.3631</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5754</v>
+        <v>0.6892</v>
       </c>
     </row>
     <row r="53">
@@ -2217,10 +2217,10 @@
         <v>60</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6333</v>
+        <v>0.6956</v>
       </c>
       <c r="G53" t="n">
-        <v>0.61</v>
+        <v>0.6767</v>
       </c>
       <c r="H53" t="n">
         <v>0.9267</v>
@@ -2251,13 +2251,13 @@
         <v>195</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3099</v>
+        <v>0.2985</v>
       </c>
       <c r="G54" t="n">
-        <v>0.4871</v>
+        <v>0.4749</v>
       </c>
       <c r="H54" t="n">
-        <v>0.7958</v>
+        <v>0.7713</v>
       </c>
     </row>
     <row r="55">
@@ -2285,13 +2285,13 @@
         <v>70</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1162</v>
+        <v>-0.1181</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1528</v>
+        <v>0.1514</v>
       </c>
       <c r="H55" t="n">
-        <v>0.6657</v>
+        <v>0.5857</v>
       </c>
     </row>
     <row r="56">
@@ -2319,13 +2319,13 @@
         <v>65</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3441</v>
+        <v>0.3026</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5446</v>
       </c>
       <c r="H56" t="n">
-        <v>0.7611</v>
+        <v>0.7907999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -2353,13 +2353,13 @@
         <v>60</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7667</v>
+        <v>0.78</v>
       </c>
       <c r="G57" t="n">
-        <v>0.7933</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>0.9833</v>
+        <v>0.9667</v>
       </c>
     </row>
     <row r="58">
@@ -2387,13 +2387,13 @@
         <v>195</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9234</v>
+        <v>0.8913</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9313</v>
+        <v>0.9015</v>
       </c>
       <c r="H58" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
     </row>
     <row r="59">
@@ -2421,13 +2421,13 @@
         <v>70</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9771</v>
+        <v>0.8724</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9657</v>
+        <v>0.8829</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0.9714</v>
       </c>
     </row>
     <row r="60">
@@ -2455,10 +2455,10 @@
         <v>65</v>
       </c>
       <c r="F60" t="n">
-        <v>0.959</v>
+        <v>0.9446</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9692</v>
+        <v>0.9538</v>
       </c>
       <c r="H60" t="n">
         <v>1</v>
@@ -2489,13 +2489,13 @@
         <v>60</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8222</v>
+        <v>0.8556</v>
       </c>
       <c r="G61" t="n">
-        <v>0.85</v>
+        <v>0.8667</v>
       </c>
       <c r="H61" t="n">
-        <v>0.95</v>
+        <v>0.9667</v>
       </c>
     </row>
     <row r="62">
@@ -2520,16 +2520,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1849</v>
+        <v>0.1788</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3634</v>
+        <v>0.3979</v>
       </c>
       <c r="H62" t="n">
-        <v>0.7</v>
+        <v>0.7026</v>
       </c>
     </row>
     <row r="63">
@@ -2554,16 +2554,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.0388</v>
+        <v>-0.2</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2507</v>
+        <v>0.1914</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6119</v>
+        <v>0.5229</v>
       </c>
     </row>
     <row r="64">
@@ -2588,16 +2588,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.0169</v>
+        <v>0.1097</v>
       </c>
       <c r="G64" t="n">
-        <v>0.2407</v>
+        <v>0.3631</v>
       </c>
       <c r="H64" t="n">
-        <v>0.5695</v>
+        <v>0.6892</v>
       </c>
     </row>
     <row r="65">
@@ -2625,10 +2625,10 @@
         <v>60</v>
       </c>
       <c r="F65" t="n">
-        <v>0.6333</v>
+        <v>0.6956</v>
       </c>
       <c r="G65" t="n">
-        <v>0.61</v>
+        <v>0.6767</v>
       </c>
       <c r="H65" t="n">
         <v>0.9267</v>
@@ -2656,16 +2656,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3161</v>
+        <v>0.2985</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4882</v>
+        <v>0.4749</v>
       </c>
       <c r="H66" t="n">
-        <v>0.7968</v>
+        <v>0.7713</v>
       </c>
     </row>
     <row r="67">
@@ -2690,16 +2690,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.1164</v>
+        <v>-0.1181</v>
       </c>
       <c r="G67" t="n">
-        <v>0.1552</v>
+        <v>0.1514</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6657</v>
+        <v>0.5857</v>
       </c>
     </row>
     <row r="68">
@@ -2724,16 +2724,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3492</v>
+        <v>0.3026</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5446</v>
       </c>
       <c r="H68" t="n">
-        <v>0.7559</v>
+        <v>0.7907999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -2761,13 +2761,13 @@
         <v>60</v>
       </c>
       <c r="F69" t="n">
-        <v>0.7667</v>
+        <v>0.78</v>
       </c>
       <c r="G69" t="n">
-        <v>0.7933</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9833</v>
+        <v>0.9667</v>
       </c>
     </row>
     <row r="70">
@@ -2792,16 +2792,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9233</v>
+        <v>0.8913</v>
       </c>
       <c r="G70" t="n">
-        <v>0.9333</v>
+        <v>0.9015</v>
       </c>
       <c r="H70" t="n">
-        <v>0.9839</v>
+        <v>0.9795</v>
       </c>
     </row>
     <row r="71">
@@ -2826,16 +2826,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9761</v>
+        <v>0.8724</v>
       </c>
       <c r="G71" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.8829</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>0.9714</v>
       </c>
     </row>
     <row r="72">
@@ -2860,13 +2860,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9661</v>
+        <v>0.9446</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9831</v>
+        <v>0.9538</v>
       </c>
       <c r="H72" t="n">
         <v>1</v>
@@ -2897,13 +2897,13 @@
         <v>60</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8222</v>
+        <v>0.8556</v>
       </c>
       <c r="G73" t="n">
-        <v>0.85</v>
+        <v>0.8667</v>
       </c>
       <c r="H73" t="n">
-        <v>0.95</v>
+        <v>0.9667</v>
       </c>
     </row>
     <row r="74">
@@ -2931,13 +2931,13 @@
         <v>195</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0407</v>
+        <v>0.0325</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3333</v>
+        <v>0.3405</v>
       </c>
       <c r="H74" t="n">
-        <v>0.6646</v>
+        <v>0.6656</v>
       </c>
     </row>
     <row r="75">
@@ -2965,13 +2965,13 @@
         <v>70</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1352</v>
+        <v>0.0914</v>
       </c>
       <c r="G75" t="n">
-        <v>0.3971</v>
+        <v>0.3457</v>
       </c>
       <c r="H75" t="n">
-        <v>0.7571</v>
+        <v>0.7171</v>
       </c>
     </row>
     <row r="76">
@@ -2999,13 +2999,13 @@
         <v>65</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.1467</v>
+        <v>-0.1138</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2677</v>
+        <v>0.3385</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5569</v>
+        <v>0.6092</v>
       </c>
     </row>
     <row r="77">
@@ -3033,13 +3033,13 @@
         <v>60</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1333</v>
+        <v>0.1222</v>
       </c>
       <c r="G77" t="n">
-        <v>0.33</v>
+        <v>0.3367</v>
       </c>
       <c r="H77" t="n">
-        <v>0.6733</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="78">
@@ -3067,13 +3067,13 @@
         <v>195</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2725</v>
+        <v>0.2342</v>
       </c>
       <c r="G78" t="n">
-        <v>0.4738</v>
+        <v>0.4646</v>
       </c>
       <c r="H78" t="n">
-        <v>0.7651</v>
+        <v>0.7631</v>
       </c>
     </row>
     <row r="79">
@@ -3101,13 +3101,13 @@
         <v>70</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2648</v>
+        <v>0.2019</v>
       </c>
       <c r="G79" t="n">
-        <v>0.4686</v>
+        <v>0.4029</v>
       </c>
       <c r="H79" t="n">
-        <v>0.7743</v>
+        <v>0.7629</v>
       </c>
     </row>
     <row r="80">
@@ -3135,13 +3135,13 @@
         <v>65</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.0482</v>
+        <v>-0.0728</v>
       </c>
       <c r="G80" t="n">
-        <v>0.3046</v>
+        <v>0.3262</v>
       </c>
       <c r="H80" t="n">
-        <v>0.5938</v>
+        <v>0.6123</v>
       </c>
     </row>
     <row r="81">
@@ -3169,13 +3169,13 @@
         <v>60</v>
       </c>
       <c r="F81" t="n">
-        <v>0.6289</v>
+        <v>0.6044</v>
       </c>
       <c r="G81" t="n">
-        <v>0.6633</v>
+        <v>0.6867</v>
       </c>
       <c r="H81" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9267</v>
       </c>
     </row>
     <row r="82">
@@ -3200,16 +3200,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F82" t="n">
-        <v>0.8974</v>
+        <v>0.8819</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9173</v>
+        <v>0.9035</v>
       </c>
       <c r="H82" t="n">
-        <v>0.9813</v>
+        <v>0.9787</v>
       </c>
     </row>
     <row r="83">
@@ -3234,16 +3234,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9429</v>
+        <v>0.8589</v>
       </c>
       <c r="G83" t="n">
-        <v>0.9399</v>
+        <v>0.8922</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="84">
@@ -3271,10 +3271,10 @@
         <v>65</v>
       </c>
       <c r="F84" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9487</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9877</v>
+        <v>0.9631</v>
       </c>
       <c r="H84" t="n">
         <v>1</v>
@@ -3305,13 +3305,13 @@
         <v>60</v>
       </c>
       <c r="F85" t="n">
-        <v>0.7867</v>
+        <v>0.8294</v>
       </c>
       <c r="G85" t="n">
-        <v>0.8233</v>
+        <v>0.8485</v>
       </c>
       <c r="H85" t="n">
-        <v>0.9467</v>
+        <v>0.9462</v>
       </c>
     </row>
     <row r="86">
@@ -3336,16 +3336,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0405</v>
+        <v>0.0321</v>
       </c>
       <c r="G86" t="n">
-        <v>0.333</v>
+        <v>0.3399</v>
       </c>
       <c r="H86" t="n">
-        <v>0.6639</v>
+        <v>0.6653</v>
       </c>
     </row>
     <row r="87">
@@ -3370,16 +3370,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1362</v>
+        <v>0.0922</v>
       </c>
       <c r="G87" t="n">
-        <v>0.3971</v>
+        <v>0.3441</v>
       </c>
       <c r="H87" t="n">
-        <v>0.7565</v>
+        <v>0.7176</v>
       </c>
     </row>
     <row r="88">
@@ -3407,13 +3407,13 @@
         <v>65</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.1467</v>
+        <v>-0.1138</v>
       </c>
       <c r="G88" t="n">
-        <v>0.2677</v>
+        <v>0.3385</v>
       </c>
       <c r="H88" t="n">
-        <v>0.5569</v>
+        <v>0.6092</v>
       </c>
     </row>
     <row r="89">
@@ -3441,13 +3441,13 @@
         <v>60</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1333</v>
+        <v>0.1222</v>
       </c>
       <c r="G89" t="n">
-        <v>0.33</v>
+        <v>0.3367</v>
       </c>
       <c r="H89" t="n">
-        <v>0.6733</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="90">
@@ -3472,16 +3472,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F90" t="n">
-        <v>0.2694</v>
+        <v>0.2366</v>
       </c>
       <c r="G90" t="n">
-        <v>0.4722</v>
+        <v>0.4653</v>
       </c>
       <c r="H90" t="n">
-        <v>0.7639</v>
+        <v>0.7627</v>
       </c>
     </row>
     <row r="91">
@@ -3506,16 +3506,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F91" t="n">
-        <v>0.256</v>
+        <v>0.2078</v>
       </c>
       <c r="G91" t="n">
-        <v>0.4638</v>
+        <v>0.4029</v>
       </c>
       <c r="H91" t="n">
-        <v>0.771</v>
+        <v>0.7618</v>
       </c>
     </row>
     <row r="92">
@@ -3543,13 +3543,13 @@
         <v>65</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.0482</v>
+        <v>-0.0728</v>
       </c>
       <c r="G92" t="n">
-        <v>0.3046</v>
+        <v>0.3262</v>
       </c>
       <c r="H92" t="n">
-        <v>0.5938</v>
+        <v>0.6123</v>
       </c>
     </row>
     <row r="93">
@@ -3577,13 +3577,13 @@
         <v>60</v>
       </c>
       <c r="F93" t="n">
-        <v>0.6289</v>
+        <v>0.6044</v>
       </c>
       <c r="G93" t="n">
-        <v>0.6633</v>
+        <v>0.6867</v>
       </c>
       <c r="H93" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9267</v>
       </c>
     </row>
     <row r="94">
@@ -3608,16 +3608,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F94" t="n">
-        <v>0.8974</v>
+        <v>0.8819</v>
       </c>
       <c r="G94" t="n">
-        <v>0.9173</v>
+        <v>0.9035</v>
       </c>
       <c r="H94" t="n">
-        <v>0.9813</v>
+        <v>0.9787</v>
       </c>
     </row>
     <row r="95">
@@ -3642,16 +3642,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F95" t="n">
-        <v>0.9429</v>
+        <v>0.8589</v>
       </c>
       <c r="G95" t="n">
-        <v>0.9399</v>
+        <v>0.8922</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="96">
@@ -3679,10 +3679,10 @@
         <v>65</v>
       </c>
       <c r="F96" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9487</v>
       </c>
       <c r="G96" t="n">
-        <v>0.9877</v>
+        <v>0.9631</v>
       </c>
       <c r="H96" t="n">
         <v>1</v>
@@ -3713,13 +3713,13 @@
         <v>60</v>
       </c>
       <c r="F97" t="n">
-        <v>0.7867</v>
+        <v>0.8294</v>
       </c>
       <c r="G97" t="n">
-        <v>0.8233</v>
+        <v>0.8485</v>
       </c>
       <c r="H97" t="n">
-        <v>0.9467</v>
+        <v>0.9462</v>
       </c>
     </row>
     <row r="98">
@@ -3744,16 +3744,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0061</v>
+        <v>0.0118</v>
       </c>
       <c r="G98" t="n">
-        <v>0.3021</v>
+        <v>0.3294</v>
       </c>
       <c r="H98" t="n">
-        <v>0.6312</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="99">
@@ -3778,16 +3778,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F99" t="n">
-        <v>0.15</v>
+        <v>0.0925</v>
       </c>
       <c r="G99" t="n">
-        <v>0.3375</v>
+        <v>0.329</v>
       </c>
       <c r="H99" t="n">
-        <v>0.775</v>
+        <v>0.7161</v>
       </c>
     </row>
     <row r="100">
@@ -3815,13 +3815,13 @@
         <v>65</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.1467</v>
+        <v>-0.1138</v>
       </c>
       <c r="G100" t="n">
-        <v>0.2677</v>
+        <v>0.3385</v>
       </c>
       <c r="H100" t="n">
-        <v>0.5569</v>
+        <v>0.6092</v>
       </c>
     </row>
     <row r="101">
@@ -3846,16 +3846,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F101" t="n">
-        <v>0.1333</v>
+        <v>0.1111</v>
       </c>
       <c r="G101" t="n">
-        <v>0.33</v>
+        <v>0.3193</v>
       </c>
       <c r="H101" t="n">
-        <v>0.6733</v>
+        <v>0.6632</v>
       </c>
     </row>
     <row r="102">
@@ -3880,16 +3880,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F102" t="n">
-        <v>0.2634</v>
+        <v>0.2227</v>
       </c>
       <c r="G102" t="n">
-        <v>0.4638</v>
+        <v>0.468</v>
       </c>
       <c r="H102" t="n">
-        <v>0.7532</v>
+        <v>0.7569</v>
       </c>
     </row>
     <row r="103">
@@ -3914,16 +3914,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1583</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G103" t="n">
-        <v>0.3625</v>
+        <v>0.329</v>
       </c>
       <c r="H103" t="n">
-        <v>0.7</v>
+        <v>0.7032</v>
       </c>
     </row>
     <row r="104">
@@ -3951,13 +3951,13 @@
         <v>65</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.0482</v>
+        <v>-0.0728</v>
       </c>
       <c r="G104" t="n">
-        <v>0.3046</v>
+        <v>0.3262</v>
       </c>
       <c r="H104" t="n">
-        <v>0.5938</v>
+        <v>0.6123</v>
       </c>
     </row>
     <row r="105">
@@ -3982,16 +3982,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F105" t="n">
-        <v>0.6289</v>
+        <v>0.6421</v>
       </c>
       <c r="G105" t="n">
-        <v>0.6633</v>
+        <v>0.7053</v>
       </c>
       <c r="H105" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9509</v>
       </c>
     </row>
     <row r="106">
@@ -4016,16 +4016,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F106" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.8928</v>
       </c>
       <c r="G106" t="n">
-        <v>0.9121</v>
+        <v>0.9163</v>
       </c>
       <c r="H106" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9791</v>
       </c>
     </row>
     <row r="107">
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F107" t="n">
-        <v>0.9167</v>
+        <v>0.8882</v>
       </c>
       <c r="G107" t="n">
-        <v>0.9375</v>
+        <v>0.929</v>
       </c>
       <c r="H107" t="n">
         <v>1</v>
@@ -4087,10 +4087,10 @@
         <v>65</v>
       </c>
       <c r="F108" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9487</v>
       </c>
       <c r="G108" t="n">
-        <v>0.9877</v>
+        <v>0.9631</v>
       </c>
       <c r="H108" t="n">
         <v>1</v>
@@ -4118,16 +4118,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F109" t="n">
-        <v>0.7867</v>
+        <v>0.8316</v>
       </c>
       <c r="G109" t="n">
-        <v>0.8233</v>
+        <v>0.8561</v>
       </c>
       <c r="H109" t="n">
-        <v>0.9467</v>
+        <v>0.9439</v>
       </c>
     </row>
     <row r="110">
@@ -4155,13 +4155,13 @@
         <v>195</v>
       </c>
       <c r="F110" t="n">
-        <v>0.01</v>
+        <v>0.0055</v>
       </c>
       <c r="G110" t="n">
-        <v>0.3001</v>
+        <v>0.3112</v>
       </c>
       <c r="H110" t="n">
-        <v>0.6773</v>
+        <v>0.6722</v>
       </c>
     </row>
     <row r="111">
@@ -4189,13 +4189,13 @@
         <v>70</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.0027</v>
+        <v>-0.0147</v>
       </c>
       <c r="G111" t="n">
-        <v>0.3265</v>
+        <v>0.3038</v>
       </c>
       <c r="H111" t="n">
-        <v>0.6735</v>
+        <v>0.6371</v>
       </c>
     </row>
     <row r="112">
@@ -4223,13 +4223,13 @@
         <v>65</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.0309</v>
+        <v>-0.0544</v>
       </c>
       <c r="G112" t="n">
-        <v>0.2315</v>
+        <v>0.2462</v>
       </c>
       <c r="H112" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6831</v>
       </c>
     </row>
     <row r="113">
@@ -4257,13 +4257,13 @@
         <v>60</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0689</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="G113" t="n">
-        <v>0.3433</v>
+        <v>0.39</v>
       </c>
       <c r="H113" t="n">
-        <v>0.6833</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="114">
@@ -4291,13 +4291,13 @@
         <v>195</v>
       </c>
       <c r="F114" t="n">
-        <v>0.2082</v>
+        <v>0.1474</v>
       </c>
       <c r="G114" t="n">
-        <v>0.4656</v>
+        <v>0.439</v>
       </c>
       <c r="H114" t="n">
-        <v>0.7805</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="115">
@@ -4325,13 +4325,13 @@
         <v>70</v>
       </c>
       <c r="F115" t="n">
-        <v>0.16</v>
+        <v>0.059</v>
       </c>
       <c r="G115" t="n">
-        <v>0.4114</v>
+        <v>0.3543</v>
       </c>
       <c r="H115" t="n">
-        <v>0.7714</v>
+        <v>0.7457</v>
       </c>
     </row>
     <row r="116">
@@ -4359,13 +4359,13 @@
         <v>65</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2308</v>
+        <v>0.1487</v>
       </c>
       <c r="G116" t="n">
-        <v>0.52</v>
+        <v>0.4738</v>
       </c>
       <c r="H116" t="n">
-        <v>0.8092</v>
+        <v>0.7477</v>
       </c>
     </row>
     <row r="117">
@@ -4393,13 +4393,13 @@
         <v>60</v>
       </c>
       <c r="F117" t="n">
-        <v>0.24</v>
+        <v>0.2489</v>
       </c>
       <c r="G117" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="H117" t="n">
-        <v>0.76</v>
+        <v>0.7233000000000001</v>
       </c>
     </row>
     <row r="118">
@@ -4427,13 +4427,13 @@
         <v>195</v>
       </c>
       <c r="F118" t="n">
-        <v>0.8801</v>
+        <v>0.8359</v>
       </c>
       <c r="G118" t="n">
-        <v>0.8972</v>
+        <v>0.8646</v>
       </c>
       <c r="H118" t="n">
-        <v>0.9692</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="119">
@@ -4461,13 +4461,13 @@
         <v>70</v>
       </c>
       <c r="F119" t="n">
-        <v>0.8813</v>
+        <v>0.7543</v>
       </c>
       <c r="G119" t="n">
-        <v>0.8737</v>
+        <v>0.7743</v>
       </c>
       <c r="H119" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9371</v>
       </c>
     </row>
     <row r="120">
@@ -4495,13 +4495,13 @@
         <v>65</v>
       </c>
       <c r="F120" t="n">
-        <v>0.9056</v>
+        <v>0.9077</v>
       </c>
       <c r="G120" t="n">
-        <v>0.9292</v>
+        <v>0.9385</v>
       </c>
       <c r="H120" t="n">
-        <v>0.9815</v>
+        <v>0.9877</v>
       </c>
     </row>
     <row r="121">
@@ -4529,13 +4529,13 @@
         <v>60</v>
       </c>
       <c r="F121" t="n">
-        <v>0.8511</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="G121" t="n">
         <v>0.89</v>
       </c>
       <c r="H121" t="n">
-        <v>0.9533</v>
+        <v>0.9567</v>
       </c>
     </row>
     <row r="122">
@@ -4563,13 +4563,13 @@
         <v>195</v>
       </c>
       <c r="F122" t="n">
-        <v>0.01</v>
+        <v>0.0055</v>
       </c>
       <c r="G122" t="n">
-        <v>0.3001</v>
+        <v>0.3112</v>
       </c>
       <c r="H122" t="n">
-        <v>0.6773</v>
+        <v>0.6722</v>
       </c>
     </row>
     <row r="123">
@@ -4597,13 +4597,13 @@
         <v>70</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.0027</v>
+        <v>-0.0147</v>
       </c>
       <c r="G123" t="n">
-        <v>0.3265</v>
+        <v>0.3038</v>
       </c>
       <c r="H123" t="n">
-        <v>0.6735</v>
+        <v>0.6371</v>
       </c>
     </row>
     <row r="124">
@@ -4631,13 +4631,13 @@
         <v>65</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.0309</v>
+        <v>-0.0544</v>
       </c>
       <c r="G124" t="n">
-        <v>0.2315</v>
+        <v>0.2462</v>
       </c>
       <c r="H124" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6831</v>
       </c>
     </row>
     <row r="125">
@@ -4665,13 +4665,13 @@
         <v>60</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0689</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="G125" t="n">
-        <v>0.3433</v>
+        <v>0.39</v>
       </c>
       <c r="H125" t="n">
-        <v>0.6833</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="126">
@@ -4699,13 +4699,13 @@
         <v>195</v>
       </c>
       <c r="F126" t="n">
-        <v>0.2082</v>
+        <v>0.1474</v>
       </c>
       <c r="G126" t="n">
-        <v>0.4656</v>
+        <v>0.439</v>
       </c>
       <c r="H126" t="n">
-        <v>0.7805</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="127">
@@ -4733,13 +4733,13 @@
         <v>70</v>
       </c>
       <c r="F127" t="n">
-        <v>0.16</v>
+        <v>0.059</v>
       </c>
       <c r="G127" t="n">
-        <v>0.4114</v>
+        <v>0.3543</v>
       </c>
       <c r="H127" t="n">
-        <v>0.7714</v>
+        <v>0.7457</v>
       </c>
     </row>
     <row r="128">
@@ -4767,13 +4767,13 @@
         <v>65</v>
       </c>
       <c r="F128" t="n">
-        <v>0.2308</v>
+        <v>0.1487</v>
       </c>
       <c r="G128" t="n">
-        <v>0.52</v>
+        <v>0.4738</v>
       </c>
       <c r="H128" t="n">
-        <v>0.8092</v>
+        <v>0.7477</v>
       </c>
     </row>
     <row r="129">
@@ -4801,13 +4801,13 @@
         <v>60</v>
       </c>
       <c r="F129" t="n">
-        <v>0.24</v>
+        <v>0.2489</v>
       </c>
       <c r="G129" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="H129" t="n">
-        <v>0.76</v>
+        <v>0.7233000000000001</v>
       </c>
     </row>
     <row r="130">
@@ -4835,13 +4835,13 @@
         <v>195</v>
       </c>
       <c r="F130" t="n">
-        <v>0.8801</v>
+        <v>0.8359</v>
       </c>
       <c r="G130" t="n">
-        <v>0.8972</v>
+        <v>0.8646</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9692</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="131">
@@ -4869,13 +4869,13 @@
         <v>70</v>
       </c>
       <c r="F131" t="n">
-        <v>0.8813</v>
+        <v>0.7543</v>
       </c>
       <c r="G131" t="n">
-        <v>0.8737</v>
+        <v>0.7743</v>
       </c>
       <c r="H131" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9371</v>
       </c>
     </row>
     <row r="132">
@@ -4903,13 +4903,13 @@
         <v>65</v>
       </c>
       <c r="F132" t="n">
-        <v>0.9056</v>
+        <v>0.9077</v>
       </c>
       <c r="G132" t="n">
-        <v>0.9292</v>
+        <v>0.9385</v>
       </c>
       <c r="H132" t="n">
-        <v>0.9815</v>
+        <v>0.9877</v>
       </c>
     </row>
     <row r="133">
@@ -4937,13 +4937,13 @@
         <v>60</v>
       </c>
       <c r="F133" t="n">
-        <v>0.8511</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="G133" t="n">
         <v>0.89</v>
       </c>
       <c r="H133" t="n">
-        <v>0.9533</v>
+        <v>0.9567</v>
       </c>
     </row>
     <row r="134">
@@ -4968,16 +4968,16 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0164</v>
+        <v>0.0068</v>
       </c>
       <c r="G134" t="n">
-        <v>0.3026</v>
+        <v>0.3112</v>
       </c>
       <c r="H134" t="n">
-        <v>0.6796</v>
+        <v>0.6738</v>
       </c>
     </row>
     <row r="135">
@@ -5002,16 +5002,16 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F135" t="n">
-        <v>0.007</v>
+        <v>-0.0129</v>
       </c>
       <c r="G135" t="n">
-        <v>0.3313</v>
+        <v>0.3032</v>
       </c>
       <c r="H135" t="n">
-        <v>0.6776</v>
+        <v>0.6387</v>
       </c>
     </row>
     <row r="136">
@@ -5036,16 +5036,16 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.0229</v>
+        <v>-0.0544</v>
       </c>
       <c r="G136" t="n">
-        <v>0.2344</v>
+        <v>0.2462</v>
       </c>
       <c r="H136" t="n">
-        <v>0.6781</v>
+        <v>0.6831</v>
       </c>
     </row>
     <row r="137">
@@ -5073,13 +5073,13 @@
         <v>60</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0689</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="G137" t="n">
-        <v>0.3433</v>
+        <v>0.39</v>
       </c>
       <c r="H137" t="n">
-        <v>0.6833</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="138">
@@ -5104,16 +5104,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F138" t="n">
-        <v>0.2</v>
+        <v>0.1622</v>
       </c>
       <c r="G138" t="n">
-        <v>0.4586</v>
+        <v>0.4513</v>
       </c>
       <c r="H138" t="n">
-        <v>0.778</v>
+        <v>0.7422</v>
       </c>
     </row>
     <row r="139">
@@ -5138,16 +5138,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F139" t="n">
-        <v>0.1443</v>
+        <v>0.0925</v>
       </c>
       <c r="G139" t="n">
-        <v>0.397</v>
+        <v>0.3806</v>
       </c>
       <c r="H139" t="n">
-        <v>0.7672</v>
+        <v>0.7548</v>
       </c>
     </row>
     <row r="140">
@@ -5172,16 +5172,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2208</v>
+        <v>0.1487</v>
       </c>
       <c r="G140" t="n">
-        <v>0.5125</v>
+        <v>0.4738</v>
       </c>
       <c r="H140" t="n">
-        <v>0.8063</v>
+        <v>0.7477</v>
       </c>
     </row>
     <row r="141">
@@ -5209,13 +5209,13 @@
         <v>60</v>
       </c>
       <c r="F141" t="n">
-        <v>0.24</v>
+        <v>0.2489</v>
       </c>
       <c r="G141" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="H141" t="n">
-        <v>0.76</v>
+        <v>0.7233000000000001</v>
       </c>
     </row>
     <row r="142">
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F142" t="n">
-        <v>0.882</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="G142" t="n">
-        <v>0.8995</v>
+        <v>0.8706</v>
       </c>
       <c r="H142" t="n">
-        <v>0.9696</v>
+        <v>0.9647</v>
       </c>
     </row>
     <row r="143">
@@ -5274,16 +5274,16 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F143" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.772</v>
       </c>
       <c r="G143" t="n">
-        <v>0.8806</v>
+        <v>0.7806</v>
       </c>
       <c r="H143" t="n">
-        <v>0.9731</v>
+        <v>0.9484</v>
       </c>
     </row>
     <row r="144">
@@ -5308,16 +5308,16 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F144" t="n">
-        <v>0.9042</v>
+        <v>0.9077</v>
       </c>
       <c r="G144" t="n">
-        <v>0.9281</v>
+        <v>0.9385</v>
       </c>
       <c r="H144" t="n">
-        <v>0.9812</v>
+        <v>0.9877</v>
       </c>
     </row>
     <row r="145">
@@ -5345,13 +5345,13 @@
         <v>60</v>
       </c>
       <c r="F145" t="n">
-        <v>0.8511</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="G145" t="n">
         <v>0.89</v>
       </c>
       <c r="H145" t="n">
-        <v>0.9533</v>
+        <v>0.9567</v>
       </c>
     </row>
   </sheetData>
